--- a/InputData/indst/_cement/CRSW/Cement Overhaul Shareweight.xlsx
+++ b/InputData/indst/_cement/CRSW/Cement Overhaul Shareweight.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CRSW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C57854-77DA-4580-B1BB-E6109DD456B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D59D87C-1306-42C4-BA66-6DEEBE2E4CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>CRSW Cement Overhaul Shareweight</t>
   </si>
@@ -67,21 +67,6 @@
     <t>alternative chemistry cement</t>
   </si>
   <si>
-    <t>Fleet age used as the calibration check</t>
-  </si>
-  <si>
-    <t>Portland Cement Association (PCA)</t>
-  </si>
-  <si>
-    <t>U.S. cement kiln fleet age statistics</t>
-  </si>
-  <si>
-    <t>(no public link)</t>
-  </si>
-  <si>
-    <t>The calibration is compared with a U.S. fleet mean operating age of about 36 years, attributed to PCA (2019).</t>
-  </si>
-  <si>
     <t>Campaign length used in the calibration</t>
   </si>
   <si>
@@ -92,9 +77,6 @@
   </si>
   <si>
     <t>InputData/indst/_cement/CPPL (EPS input file)</t>
-  </si>
-  <si>
-    <t>A campaign length of 25 years, the average time between overhaul decisions. The mean retirement age that the weight produces depends on this value, so the weight should be re-checked if CPPL changes.</t>
   </si>
   <si>
     <t>Purpose and layout</t>
@@ -107,23 +89,71 @@
     <t>U.S. values</t>
   </si>
   <si>
-    <t>The weight is 0.129678, the same for all four pathways and every year. It is a calibration setting, not a market observation. We chose it so that, in the business-as-usual run, the average overhaul share of dry kiln capacity reaching a decision over 2026-2050 is about 0.485 (the model result is 0.4857). That corresponds to kilns retiring at a mean age of roughly 49 years with a 25-year campaign length, which we judge a reasonable match to the long lives of U.S. kilns; for comparison, the fleet's mean operating age is about 36 years. The target share is our judgment.</t>
-  </si>
-  <si>
     <t>Keeping it in step with other inputs</t>
   </si>
   <si>
-    <t>The right weight depends on the cost comparison it multiplies, so it should be re-solved if the capital costs of new kilns or overhauls (CPCC and CRCC), the campaign length (CPPL), or the fuel and technology choice settings change. The other three pathways use the same weight as the dry kiln; the calibration only constrains the dry kiln, so that is also our judgment. With the default CCS subsidy (a 45Q-type credit), the business-as-usual run builds some CCS kilns from about 2030, because the subsidy exceeds the cost of capture, transport, storage, and energy; this affects which replacement choices the weight acts on.</t>
-  </si>
-  <si>
     <t>Unit: dimensionless</t>
+  </si>
+  <si>
+    <t>U.S. kiln fleet age</t>
+  </si>
+  <si>
+    <t>Princeton University, Net-Zero America project</t>
+  </si>
+  <si>
+    <t>Net-Zero America, Annex K (Cement industry), p. 22</t>
+  </si>
+  <si>
+    <t>https://netzeroamerica.princeton.edu/img/NZA%20Annex%20K%20-%20Cement%20industry.pdf</t>
+  </si>
+  <si>
+    <t>The unretired U.S. kiln fleet averaged 36 years old in 2018, built from the Portland Cement Association's 2016 Plant Information Summary and EPA greenhouse gas reporting data (92 kilns from before 2000, average install or modernization year 1972; 38 kilns since 2000, average 2005). Weighted by capacity instead of kiln count, the average is about 30 years.</t>
+  </si>
+  <si>
+    <t>Kiln counts and closures over time</t>
+  </si>
+  <si>
+    <t>U.S. Geological Survey</t>
+  </si>
+  <si>
+    <t>Minerals Yearbook, Cement chapters (2000, 2005, 2010, 2022)</t>
+  </si>
+  <si>
+    <t>https://www.usgs.gov/centers/national-minerals-information-center/cement-statistics-and-information</t>
+  </si>
+  <si>
+    <t>U.S. kilns fell from 199 in 2000 to 185 (2005), 153 (2010) and 126 (2022) while capacity stayed roughly flat, which reflects consolidation and the retirement of wet and long dry kilns. From 2000 to 2018, older kilns left the fleet at roughly 3.3% of capacity a year.</t>
+  </si>
+  <si>
+    <t>Plant ages today</t>
+  </si>
+  <si>
+    <t>Global Energy Monitor</t>
+  </si>
+  <si>
+    <t>Global Cement and Concrete Tracker (July 2026 public map data)</t>
+  </si>
+  <si>
+    <t>https://globalenergymonitor.org/projects/global-cement-and-concrete-tracker/</t>
+  </si>
+  <si>
+    <t>58% of U.S. operating capacity is at sites more than 50 years old (64 of 96 plants). These are site start years, not kiln years, so they show that U.S. sites keep running through brownfield replacement lines.</t>
+  </si>
+  <si>
+    <t>A campaign length of 25 years, the average time between overhaul decisions. The mean retirement age that the weight produces depends on this value.</t>
+  </si>
+  <si>
+    <t>The right weight depends on the cost comparison it multiplies, so it should be re-solved whenever the capital costs of new kilns or overhauls (the CPCaOC file), the campaign length (CPPL), or the fuel and technology choice settings change. The other three pathways use the same weight as the dry kiln; the calibration only constrains the dry kiln, so that is our judgment. The 2026-2050 decisions fall mostly on kilns that will then be 50-75 years old; if real retirement odds rise with age, a single weight will retire too few of them. Buying the Portland Cement Association's Plant Information Summary (kiln-age and retired-facility tables) would allow a direct estimate.</t>
+  </si>
+  <si>
+    <t>The weight is 0.097704, the same for all four pathways and every year. It is a calibration setting, not a market observation. We chose it so that, in the business-as-usual run, the average overhaul share of dry kiln capacity reaching a decision over 2026-2050 is 0.485 (the model result is 0.4848). With 25-year campaigns that means kilns retire at a mean age of about 49 years, and a fleet in steady state with that retirement pattern has an average age of about 36 years, which matches the Net-Zero America figure. Other ways of reading the data give overhaul shares of 0.41-0.57, so 0.40-0.60 is a reasonable range.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +171,22 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -169,10 +215,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -184,11 +231,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -489,112 +540,178 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="6">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B17" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B19" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B20" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B22" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B24" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="5">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B27" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B28" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
+    <row r="29" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B29" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+      <c r="B33" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
+    <row r="34" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B34" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="5">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>25</v>
+      <c r="B35" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{A029AC34-2335-430E-A61B-724B3426F6E4}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{1A4FD09B-58F5-4134-987F-D749AE688238}"/>
+    <hyperlink ref="B21" r:id="rId3" xr:uid="{221C8014-6C7D-4B52-89CC-9EF07F6FF3E7}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -602,27 +719,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>0.12967799999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9.7703999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.48570000000000002</v>
+        <v>0.48480000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -636,11 +753,11 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -733,504 +850,504 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="C2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="D2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="E2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="F2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="G2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="H2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="I2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="J2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="K2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="L2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="M2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="N2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="O2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="P2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Q2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="R2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="S2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="T2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="U2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="V2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="W2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="X2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Y2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Z2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AA2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AB2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AC2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AD2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AE2">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+        <v>9.7703999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="C3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="D3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="E3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="F3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="G3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="H3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="I3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="J3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="K3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="L3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="M3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="N3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="O3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="P3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Q3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="R3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="S3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="T3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="U3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="V3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="W3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="X3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Y3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Z3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AA3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AB3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AC3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AD3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AE3">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+        <v>9.7703999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="C4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="D4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="E4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="F4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="G4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="H4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="I4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="J4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="K4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="L4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="M4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="N4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="O4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="P4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Q4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="R4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="S4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="T4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="U4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="V4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="W4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="X4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Y4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Z4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AA4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AB4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AC4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AD4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AE4">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+        <v>9.7703999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="C5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="D5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="E5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="F5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="G5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="H5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="I5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="J5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="K5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="L5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="M5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="N5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="O5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="P5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Q5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="R5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="S5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="T5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="U5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="V5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="W5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="X5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Y5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="Z5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AA5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AB5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AC5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AD5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
       <c r="AE5">
         <f>Derivation!$B$3</f>
-        <v>0.12967799999999999</v>
+        <v>9.7703999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/indst/_cement/CRSW/Cement Overhaul Shareweight.xlsx
+++ b/InputData/indst/_cement/CRSW/Cement Overhaul Shareweight.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CRSW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D59D87C-1306-42C4-BA66-6DEEBE2E4CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087D576D-CAF4-460E-B079-F94AFD7B4621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>CRSW Cement Overhaul Shareweight</t>
   </si>
@@ -147,6 +147,15 @@
   </si>
   <si>
     <t>The weight is 0.097704, the same for all four pathways and every year. It is a calibration setting, not a market observation. We chose it so that, in the business-as-usual run, the average overhaul share of dry kiln capacity reaching a decision over 2026-2050 is 0.485 (the model result is 0.4848). With 25-year campaigns that means kilns retire at a mean age of about 49 years, and a fleet in steady state with that retirement pattern has an average age of about 36 years, which matches the Net-Zero America figure. Other ways of reading the data give overhaul shares of 0.41-0.57, so 0.40-0.60 is a reasonable range.</t>
+  </si>
+  <si>
+    <t>electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>Electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>The electric kiln with CCS is the electric kiln with a capture unit on its nearly pure CO2 stream, so it uses the electric kiln's value here (same kiln). Its capture is added through CCF (95 percent of calcination CO2 captured) and the CDSC capture inputs.</t>
   </si>
 </sst>
 </file>
@@ -219,7 +228,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -234,8 +243,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -540,21 +555,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="2" max="2" width="110.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.6328125" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="110.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -562,127 +577,127 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="6">
         <v>2021</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
         <v>2024</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" s="6">
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B27" s="6">
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
@@ -690,7 +705,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>16</v>
       </c>
@@ -698,12 +713,20 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -719,14 +742,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -734,7 +757,7 @@
         <v>9.7703999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -752,10 +775,10 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -850,7 +873,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -975,7 +998,7 @@
         <v>9.7703999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1100,7 +1123,7 @@
         <v>9.7703999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1225,127 +1248,252 @@
         <v>9.7703999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="C5">
+        <f>C4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="D5">
+        <f>D4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="E5">
+        <f>E4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="F5">
+        <f>F4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="G5">
+        <f>G4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="H5">
+        <f>H4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="I5">
+        <f>I4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="J5">
+        <f>J4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="K5">
+        <f>K4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="L5">
+        <f>L4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="M5">
+        <f>M4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="N5">
+        <f>N4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="O5">
+        <f>O4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="P5">
+        <f>P4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="Q5">
+        <f>Q4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="R5">
+        <f>R4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="S5">
+        <f>S4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="T5">
+        <f>T4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="U5">
+        <f>U4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="V5">
+        <f>V4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="W5">
+        <f>W4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="X5">
+        <f>X4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="Y5">
+        <f>Y4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="Z5">
+        <f>Z4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="AA5">
+        <f>AA4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="AB5">
+        <f>AB4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="AC5">
+        <f>AC4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="AD5">
+        <f>AD4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="AE5">
+        <f>AE4</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="C5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="D5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="E5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="F5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="G5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="H5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="I5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="J5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="K5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="L5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="M5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="N5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="O5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="P5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="Q5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="R5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="S5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="T5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="U5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="V5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="W5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="X5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="Y5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="Z5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="AA5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="AB5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="AC5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="AD5">
-        <f>Derivation!$B$3</f>
-        <v>9.7703999999999999E-2</v>
-      </c>
-      <c r="AE5">
+      <c r="B6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="C6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="D6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="E6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="F6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="G6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="H6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="I6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="J6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="K6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="L6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="M6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="N6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="O6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="P6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="Q6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="R6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="S6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="T6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="U6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="V6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="W6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="X6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="Y6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="Z6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="AA6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="AB6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="AC6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="AD6">
+        <f>Derivation!$B$3</f>
+        <v>9.7703999999999999E-2</v>
+      </c>
+      <c r="AE6">
         <f>Derivation!$B$3</f>
         <v>9.7703999999999999E-2</v>
       </c>
